--- a/artfynd/A 10909-2025 artfynd.xlsx
+++ b/artfynd/A 10909-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>88776490</v>
       </c>
       <c r="B2" t="n">
-        <v>98938</v>
+        <v>98939</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10909-2025 artfynd.xlsx
+++ b/artfynd/A 10909-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>88776490</v>
       </c>
       <c r="B2" t="n">
-        <v>98939</v>
+        <v>98941</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10909-2025 artfynd.xlsx
+++ b/artfynd/A 10909-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>88776490</v>
       </c>
       <c r="B2" t="n">
-        <v>98941</v>
+        <v>98942</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10909-2025 artfynd.xlsx
+++ b/artfynd/A 10909-2025 artfynd.xlsx
@@ -776,12 +776,7 @@
         <v>121072385</v>
       </c>
       <c r="B3" t="n">
-        <v>87987</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90028</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10909-2025 artfynd.xlsx
+++ b/artfynd/A 10909-2025 artfynd.xlsx
@@ -776,7 +776,7 @@
         <v>121072385</v>
       </c>
       <c r="B3" t="n">
-        <v>90028</v>
+        <v>90029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10909-2025 artfynd.xlsx
+++ b/artfynd/A 10909-2025 artfynd.xlsx
@@ -776,7 +776,7 @@
         <v>121072385</v>
       </c>
       <c r="B3" t="n">
-        <v>90029</v>
+        <v>90031</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10909-2025 artfynd.xlsx
+++ b/artfynd/A 10909-2025 artfynd.xlsx
@@ -776,7 +776,7 @@
         <v>121072385</v>
       </c>
       <c r="B3" t="n">
-        <v>90031</v>
+        <v>90032</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10909-2025 artfynd.xlsx
+++ b/artfynd/A 10909-2025 artfynd.xlsx
@@ -675,45 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88776490</v>
+        <v>121072385</v>
       </c>
       <c r="B2" t="n">
-        <v>98942</v>
+        <v>90093</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>953</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Arommusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Lepista densifolia</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(J.Favre) Singer &amp; Clémençon</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Alby skog 300 m Ö väg 269, Upl</t>
+          <t>Alby skog, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>649402</v>
+        <v>649413</v>
       </c>
       <c r="R2" t="n">
-        <v>6605854</v>
+        <v>6605842</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-07-08</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-07-08</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,48 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121072385</v>
+        <v>88776490</v>
       </c>
       <c r="B3" t="n">
-        <v>90037</v>
+        <v>99038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>953</v>
+        <v>223597</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arommusseron</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lepista densifolia</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(J.Favre) Singer &amp; Clémençon</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Alby skog, Upl</t>
+          <t>Alby skog 300 m Ö väg 269, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>649413</v>
+        <v>649402</v>
       </c>
       <c r="R3" t="n">
-        <v>6605842</v>
+        <v>6605854</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -841,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2020-07-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2020-07-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
